--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ232"/>
+  <dimension ref="A1:AJ233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26850,6 +26850,120 @@
         <v>322.21</v>
       </c>
       <c r="AJ232" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>377.37</v>
+      </c>
+      <c r="C233" t="n">
+        <v>346.38</v>
+      </c>
+      <c r="D233" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="E233" t="n">
+        <v>354.2</v>
+      </c>
+      <c r="F233" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="G233" t="n">
+        <v>378.27</v>
+      </c>
+      <c r="H233" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="I233" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="J233" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="K233" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="L233" t="n">
+        <v>375.17</v>
+      </c>
+      <c r="M233" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="N233" t="n">
+        <v>390.28</v>
+      </c>
+      <c r="O233" t="n">
+        <v>394.72</v>
+      </c>
+      <c r="P233" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>384.64</v>
+      </c>
+      <c r="R233" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="S233" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="T233" t="n">
+        <v>378.99</v>
+      </c>
+      <c r="U233" t="n">
+        <v>386.03</v>
+      </c>
+      <c r="V233" t="n">
+        <v>393.88</v>
+      </c>
+      <c r="W233" t="n">
+        <v>403.95</v>
+      </c>
+      <c r="X233" t="n">
+        <v>410.64</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>403.74</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>380.23</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>376.92</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>371.44</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>310.62</v>
+      </c>
+      <c r="AJ233" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26866,7 +26980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B233"/>
+  <dimension ref="A1:B234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29199,6 +29313,16 @@
       </c>
       <c r="B233" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -29367,28 +29491,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.229498190495374</v>
+        <v>-0.223383523175173</v>
       </c>
       <c r="J2" t="n">
+        <v>232</v>
+      </c>
+      <c r="K2" t="n">
         <v>231</v>
       </c>
-      <c r="K2" t="n">
-        <v>230</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02750457397851624</v>
+        <v>0.02629344297463976</v>
       </c>
       <c r="M2" t="n">
-        <v>8.126164775913743</v>
+        <v>8.120533323402464</v>
       </c>
       <c r="N2" t="n">
-        <v>127.1300389955729</v>
+        <v>126.8405227895133</v>
       </c>
       <c r="O2" t="n">
-        <v>11.27519574089838</v>
+        <v>11.2623497898757</v>
       </c>
       <c r="P2" t="n">
-        <v>375.7254961222638</v>
+        <v>375.6707096497304</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29445,28 +29569,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3863949816748242</v>
+        <v>-0.3864725766296465</v>
       </c>
       <c r="J3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L3" t="n">
-        <v>0.129927874185385</v>
+        <v>0.1310850675136002</v>
       </c>
       <c r="M3" t="n">
-        <v>6.308670785701186</v>
+        <v>6.281895626613942</v>
       </c>
       <c r="N3" t="n">
-        <v>68.39595590950128</v>
+        <v>68.10118782178688</v>
       </c>
       <c r="O3" t="n">
-        <v>8.270184756672688</v>
+        <v>8.252344383372938</v>
       </c>
       <c r="P3" t="n">
-        <v>356.8697193315757</v>
+        <v>356.8704117816224</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29523,28 +29647,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3092993010466726</v>
+        <v>-0.3067588794709908</v>
       </c>
       <c r="J4" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K4" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1047527465351393</v>
+        <v>0.1040508079308011</v>
       </c>
       <c r="M4" t="n">
-        <v>6.03695340637098</v>
+        <v>6.024728295600325</v>
       </c>
       <c r="N4" t="n">
-        <v>55.93066745400019</v>
+        <v>55.73467767848118</v>
       </c>
       <c r="O4" t="n">
-        <v>7.478680863227163</v>
+        <v>7.465566132483268</v>
       </c>
       <c r="P4" t="n">
-        <v>349.7443510816494</v>
+        <v>349.721680599494</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29601,28 +29725,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2187365550307726</v>
+        <v>-0.2129062969328192</v>
       </c>
       <c r="J5" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K5" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06028550396093579</v>
+        <v>0.05757415308323632</v>
       </c>
       <c r="M5" t="n">
-        <v>5.734787891995847</v>
+        <v>5.737029075370928</v>
       </c>
       <c r="N5" t="n">
-        <v>51.01998336652423</v>
+        <v>51.03756265691314</v>
       </c>
       <c r="O5" t="n">
-        <v>7.142827407023372</v>
+        <v>7.144057856492565</v>
       </c>
       <c r="P5" t="n">
-        <v>352.6053737408668</v>
+        <v>352.5533450683675</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29679,28 +29803,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2702784010669754</v>
+        <v>-0.2612835279020775</v>
       </c>
       <c r="J6" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K6" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06786247861705252</v>
+        <v>0.06379677718658439</v>
       </c>
       <c r="M6" t="n">
-        <v>6.585030421822619</v>
+        <v>6.602707898390274</v>
       </c>
       <c r="N6" t="n">
-        <v>68.64161617264327</v>
+        <v>68.91102940345276</v>
       </c>
       <c r="O6" t="n">
-        <v>8.285023607247192</v>
+        <v>8.301266734869611</v>
       </c>
       <c r="P6" t="n">
-        <v>359.8640890341388</v>
+        <v>359.7838196357338</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29757,28 +29881,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1221460217645674</v>
+        <v>-0.1131106692087721</v>
       </c>
       <c r="J7" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K7" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00857736334906245</v>
+        <v>0.007400625887487355</v>
       </c>
       <c r="M7" t="n">
-        <v>8.744589825804752</v>
+        <v>8.754235581046213</v>
       </c>
       <c r="N7" t="n">
-        <v>117.9718045702852</v>
+        <v>118.0336869768487</v>
       </c>
       <c r="O7" t="n">
-        <v>10.86148261381867</v>
+        <v>10.86433094934284</v>
       </c>
       <c r="P7" t="n">
-        <v>369.9704232203183</v>
+        <v>369.8897925876529</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29835,28 +29959,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1520551696174502</v>
+        <v>-0.149637189422225</v>
       </c>
       <c r="J8" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K8" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0193676163105263</v>
+        <v>0.0189397671688154</v>
       </c>
       <c r="M8" t="n">
-        <v>7.360712781251255</v>
+        <v>7.344002322992329</v>
       </c>
       <c r="N8" t="n">
-        <v>80.08422634722912</v>
+        <v>79.7798846527359</v>
       </c>
       <c r="O8" t="n">
-        <v>8.948979067314278</v>
+        <v>8.931958612350144</v>
       </c>
       <c r="P8" t="n">
-        <v>366.6375024899087</v>
+        <v>366.6159246630658</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29913,28 +30037,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3833415884444763</v>
+        <v>-0.3762226061873021</v>
       </c>
       <c r="J9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06797798443444525</v>
+        <v>0.06608501612493756</v>
       </c>
       <c r="M9" t="n">
-        <v>9.478429078101522</v>
+        <v>9.476358104477203</v>
       </c>
       <c r="N9" t="n">
-        <v>137.8301757701665</v>
+        <v>137.5901680917279</v>
       </c>
       <c r="O9" t="n">
-        <v>11.74010970009082</v>
+        <v>11.729883549794</v>
       </c>
       <c r="P9" t="n">
-        <v>366.6408283269752</v>
+        <v>366.5772992018211</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29991,28 +30115,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5192277163044549</v>
+        <v>-0.5123528069143043</v>
       </c>
       <c r="J10" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K10" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1377574027915395</v>
+        <v>0.1354305526131598</v>
       </c>
       <c r="M10" t="n">
-        <v>9.008369618097218</v>
+        <v>9.005841704276797</v>
       </c>
       <c r="N10" t="n">
-        <v>115.4369406457462</v>
+        <v>115.2695920796394</v>
       </c>
       <c r="O10" t="n">
-        <v>10.7441584428817</v>
+        <v>10.73636773213545</v>
       </c>
       <c r="P10" t="n">
-        <v>375.4766533329404</v>
+        <v>375.4153022909948</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30069,28 +30193,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6163499410306068</v>
+        <v>-0.6084451527595608</v>
       </c>
       <c r="J11" t="n">
+        <v>232</v>
+      </c>
+      <c r="K11" t="n">
         <v>231</v>
       </c>
-      <c r="K11" t="n">
-        <v>230</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1772892632746986</v>
+        <v>0.1744400939342989</v>
       </c>
       <c r="M11" t="n">
-        <v>8.939599462119315</v>
+        <v>8.942427004631195</v>
       </c>
       <c r="N11" t="n">
-        <v>121.1101445926878</v>
+        <v>121.024605361607</v>
       </c>
       <c r="O11" t="n">
-        <v>11.00500543356012</v>
+        <v>11.00111836867539</v>
       </c>
       <c r="P11" t="n">
-        <v>380.31307616491</v>
+        <v>380.2426964358171</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30147,28 +30271,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6700973748573105</v>
+        <v>-0.6618594419880625</v>
       </c>
       <c r="J12" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K12" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1743271863401945</v>
+        <v>0.1717146104632761</v>
       </c>
       <c r="M12" t="n">
-        <v>9.620121170005016</v>
+        <v>9.619369532337139</v>
       </c>
       <c r="N12" t="n">
-        <v>145.9971807369759</v>
+        <v>145.8399662030539</v>
       </c>
       <c r="O12" t="n">
-        <v>12.08292931109737</v>
+        <v>12.07642191226581</v>
       </c>
       <c r="P12" t="n">
-        <v>382.6347765989393</v>
+        <v>382.5611626491728</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30225,28 +30349,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8874136829145091</v>
+        <v>-0.8743827792145829</v>
       </c>
       <c r="J13" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K13" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2562189243990025</v>
+        <v>0.251017600395775</v>
       </c>
       <c r="M13" t="n">
-        <v>10.24278387090108</v>
+        <v>10.26352352661032</v>
       </c>
       <c r="N13" t="n">
-        <v>157.3185851194502</v>
+        <v>157.8317714008642</v>
       </c>
       <c r="O13" t="n">
-        <v>12.54267057366373</v>
+        <v>12.5631115334086</v>
       </c>
       <c r="P13" t="n">
-        <v>389.156769080396</v>
+        <v>389.0403286872937</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30303,28 +30427,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.831698027800312</v>
+        <v>-0.8164687598985015</v>
       </c>
       <c r="J14" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K14" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2943075374448202</v>
+        <v>0.2857539449003276</v>
       </c>
       <c r="M14" t="n">
-        <v>8.544841076356356</v>
+        <v>8.58538294103931</v>
       </c>
       <c r="N14" t="n">
-        <v>114.140378149302</v>
+        <v>115.2812192052211</v>
       </c>
       <c r="O14" t="n">
-        <v>10.68365003869474</v>
+        <v>10.73690920168468</v>
       </c>
       <c r="P14" t="n">
-        <v>393.1375781256069</v>
+        <v>393.0014937847213</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30381,28 +30505,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9705568102357921</v>
+        <v>-0.9527969482189856</v>
       </c>
       <c r="J15" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K15" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3468155581552903</v>
+        <v>0.3366337923069126</v>
       </c>
       <c r="M15" t="n">
-        <v>8.852194284620246</v>
+        <v>8.910118973439197</v>
       </c>
       <c r="N15" t="n">
-        <v>121.200175002268</v>
+        <v>122.8686165564189</v>
       </c>
       <c r="O15" t="n">
-        <v>11.00909510369803</v>
+        <v>11.08461170075068</v>
       </c>
       <c r="P15" t="n">
-        <v>398.3396166399273</v>
+        <v>398.1791881116516</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30459,28 +30583,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8946096853282773</v>
+        <v>-0.8828672329856957</v>
       </c>
       <c r="J16" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K16" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3243414303259933</v>
+        <v>0.3188628986252598</v>
       </c>
       <c r="M16" t="n">
-        <v>8.704376153751719</v>
+        <v>8.73117634178638</v>
       </c>
       <c r="N16" t="n">
-        <v>113.8980050756263</v>
+        <v>114.3578450150922</v>
       </c>
       <c r="O16" t="n">
-        <v>10.67230083326113</v>
+        <v>10.69382275031208</v>
       </c>
       <c r="P16" t="n">
-        <v>401.4319589209677</v>
+        <v>401.3258869061128</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30537,28 +30661,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9138564791816566</v>
+        <v>-0.9100986233473637</v>
       </c>
       <c r="J17" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K17" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L17" t="n">
-        <v>0.361349901051756</v>
+        <v>0.3614705624276671</v>
       </c>
       <c r="M17" t="n">
-        <v>8.079765594763808</v>
+        <v>8.065481799425591</v>
       </c>
       <c r="N17" t="n">
-        <v>101.1674570023852</v>
+        <v>100.8230635378092</v>
       </c>
       <c r="O17" t="n">
-        <v>10.05820346793528</v>
+        <v>10.04106884439148</v>
       </c>
       <c r="P17" t="n">
-        <v>404.425143574369</v>
+        <v>404.3913837750529</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30615,28 +30739,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.025776802856432</v>
+        <v>-1.028290465447846</v>
       </c>
       <c r="J18" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K18" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3970989713582757</v>
+        <v>0.400512408877291</v>
       </c>
       <c r="M18" t="n">
-        <v>8.429505485187248</v>
+        <v>8.405121812170455</v>
       </c>
       <c r="N18" t="n">
-        <v>109.4971484160787</v>
+        <v>109.0613389408262</v>
       </c>
       <c r="O18" t="n">
-        <v>10.46408851339087</v>
+        <v>10.44324369823984</v>
       </c>
       <c r="P18" t="n">
-        <v>407.3357213660366</v>
+        <v>407.3583035906819</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30693,28 +30817,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.065275553029081</v>
+        <v>-1.069311410918379</v>
       </c>
       <c r="J19" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K19" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4214859281181075</v>
+        <v>0.4254595321538153</v>
       </c>
       <c r="M19" t="n">
-        <v>8.466929927766872</v>
+        <v>8.45242949497484</v>
       </c>
       <c r="N19" t="n">
-        <v>106.0858980360555</v>
+        <v>105.7380753395686</v>
       </c>
       <c r="O19" t="n">
-        <v>10.29980087361185</v>
+        <v>10.28290208742496</v>
       </c>
       <c r="P19" t="n">
-        <v>408.2700985945334</v>
+        <v>408.3064108479409</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30771,28 +30895,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9559410118609016</v>
+        <v>-0.9572328248383282</v>
       </c>
       <c r="J20" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K20" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3074825955617518</v>
+        <v>0.3101324270444001</v>
       </c>
       <c r="M20" t="n">
-        <v>9.748965914099346</v>
+        <v>9.71500922842783</v>
       </c>
       <c r="N20" t="n">
-        <v>140.7948886556264</v>
+        <v>140.1996734914686</v>
       </c>
       <c r="O20" t="n">
-        <v>11.86570219816874</v>
+        <v>11.84059430482561</v>
       </c>
       <c r="P20" t="n">
-        <v>406.3599362718629</v>
+        <v>406.3714642888398</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30849,28 +30973,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.312545787838254</v>
+        <v>-1.307466282552553</v>
       </c>
       <c r="J21" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K21" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4823186753386807</v>
+        <v>0.4824714138396711</v>
       </c>
       <c r="M21" t="n">
-        <v>9.292919106328805</v>
+        <v>9.28369650224897</v>
       </c>
       <c r="N21" t="n">
-        <v>126.4945724355461</v>
+        <v>126.1296049879353</v>
       </c>
       <c r="O21" t="n">
-        <v>11.24698059194316</v>
+        <v>11.23074374153089</v>
       </c>
       <c r="P21" t="n">
-        <v>414.8182694298357</v>
+        <v>414.7729404045118</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30927,28 +31051,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.371549997115103</v>
+        <v>-1.361942770013224</v>
       </c>
       <c r="J22" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K22" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5715141475027239</v>
+        <v>0.5688300829184898</v>
       </c>
       <c r="M22" t="n">
-        <v>8.17101436053335</v>
+        <v>8.195293059526756</v>
       </c>
       <c r="N22" t="n">
-        <v>96.48223048804708</v>
+        <v>96.71122763741116</v>
       </c>
       <c r="O22" t="n">
-        <v>9.822536866209619</v>
+        <v>9.834186678999497</v>
       </c>
       <c r="P22" t="n">
-        <v>418.4519570862103</v>
+        <v>418.3662230991189</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31005,28 +31129,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.13441907574002</v>
+        <v>-1.120776972872663</v>
       </c>
       <c r="J23" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K23" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5107322406643493</v>
+        <v>0.5032923315184231</v>
       </c>
       <c r="M23" t="n">
-        <v>7.585021641973345</v>
+        <v>7.634072084035289</v>
       </c>
       <c r="N23" t="n">
-        <v>84.33637153381645</v>
+        <v>85.27313577715606</v>
       </c>
       <c r="O23" t="n">
-        <v>9.183483627350595</v>
+        <v>9.234345443893469</v>
       </c>
       <c r="P23" t="n">
-        <v>416.9685173713868</v>
+        <v>416.8467765341269</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31083,28 +31207,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.119072912722853</v>
+        <v>-1.101814145976014</v>
       </c>
       <c r="J24" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K24" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4458037929373749</v>
+        <v>0.4357660648064857</v>
       </c>
       <c r="M24" t="n">
-        <v>8.413181532733683</v>
+        <v>8.474292593297209</v>
       </c>
       <c r="N24" t="n">
-        <v>106.5003668199138</v>
+        <v>108.1224223448935</v>
       </c>
       <c r="O24" t="n">
-        <v>10.31990149274274</v>
+        <v>10.39819322502201</v>
       </c>
       <c r="P24" t="n">
-        <v>418.6105642716397</v>
+        <v>418.4565486675746</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31161,28 +31285,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.35099134777803</v>
+        <v>-1.332513470701209</v>
       </c>
       <c r="J25" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K25" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L25" t="n">
-        <v>0.547790473293317</v>
+        <v>0.5376841158576152</v>
       </c>
       <c r="M25" t="n">
-        <v>8.124263124780029</v>
+        <v>8.20447657912788</v>
       </c>
       <c r="N25" t="n">
-        <v>103.0729993353819</v>
+        <v>105.0142191649308</v>
       </c>
       <c r="O25" t="n">
-        <v>10.15248734721605</v>
+        <v>10.24764456667632</v>
       </c>
       <c r="P25" t="n">
-        <v>416.3892806511017</v>
+        <v>416.2243858216176</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31239,28 +31363,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.376204723403123</v>
+        <v>-1.360143630577822</v>
       </c>
       <c r="J26" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K26" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5047682834184066</v>
+        <v>0.4978132196456795</v>
       </c>
       <c r="M26" t="n">
-        <v>9.13491588592615</v>
+        <v>9.19681128293052</v>
       </c>
       <c r="N26" t="n">
-        <v>127.1150657918271</v>
+        <v>128.3694492815818</v>
       </c>
       <c r="O26" t="n">
-        <v>11.27453173270744</v>
+        <v>11.33002424011449</v>
       </c>
       <c r="P26" t="n">
-        <v>406.886174085002</v>
+        <v>406.7428464098721</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31317,28 +31441,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.064639823843502</v>
+        <v>-1.052338078898136</v>
       </c>
       <c r="J27" t="n">
+        <v>232</v>
+      </c>
+      <c r="K27" t="n">
         <v>231</v>
       </c>
-      <c r="K27" t="n">
-        <v>230</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.410315140939337</v>
+        <v>0.4047697097114393</v>
       </c>
       <c r="M27" t="n">
-        <v>8.43825467428192</v>
+        <v>8.477493785894207</v>
       </c>
       <c r="N27" t="n">
-        <v>111.7700400856917</v>
+        <v>112.3486396878341</v>
       </c>
       <c r="O27" t="n">
-        <v>10.57213507696963</v>
+        <v>10.59946412267309</v>
       </c>
       <c r="P27" t="n">
-        <v>393.0921743666612</v>
+        <v>392.9824596245744</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31395,28 +31519,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9840186746429737</v>
+        <v>-0.9705167068173494</v>
       </c>
       <c r="J28" t="n">
+        <v>232</v>
+      </c>
+      <c r="K28" t="n">
         <v>231</v>
       </c>
-      <c r="K28" t="n">
-        <v>230</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.3892291237717566</v>
+        <v>0.382095811695816</v>
       </c>
       <c r="M28" t="n">
-        <v>8.102336703017015</v>
+        <v>8.150517002216892</v>
       </c>
       <c r="N28" t="n">
-        <v>104.2550811999948</v>
+        <v>105.0836434707687</v>
       </c>
       <c r="O28" t="n">
-        <v>10.21053775273344</v>
+        <v>10.25103133693233</v>
       </c>
       <c r="P28" t="n">
-        <v>386.066442358437</v>
+        <v>385.9460232695816</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31473,28 +31597,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9410381901106079</v>
+        <v>-0.9271797124561098</v>
       </c>
       <c r="J29" t="n">
+        <v>232</v>
+      </c>
+      <c r="K29" t="n">
         <v>231</v>
       </c>
-      <c r="K29" t="n">
-        <v>230</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.3373753593064668</v>
+        <v>0.3304412040260827</v>
       </c>
       <c r="M29" t="n">
-        <v>8.350467261798112</v>
+        <v>8.391903281683266</v>
       </c>
       <c r="N29" t="n">
-        <v>119.3400670128389</v>
+        <v>120.171807425242</v>
       </c>
       <c r="O29" t="n">
-        <v>10.92428794076936</v>
+        <v>10.96229024543877</v>
       </c>
       <c r="P29" t="n">
-        <v>378.9771853494481</v>
+        <v>378.8535866804517</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31551,28 +31675,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7965385928044056</v>
+        <v>-0.7829320246814269</v>
       </c>
       <c r="J30" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K30" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2671809875649448</v>
+        <v>0.2602848670735558</v>
       </c>
       <c r="M30" t="n">
-        <v>8.245292317468502</v>
+        <v>8.283996950479015</v>
       </c>
       <c r="N30" t="n">
-        <v>119.047250288687</v>
+        <v>119.827633581967</v>
       </c>
       <c r="O30" t="n">
-        <v>10.91087761312934</v>
+        <v>10.94658090830041</v>
       </c>
       <c r="P30" t="n">
-        <v>373.5762273158686</v>
+        <v>373.4548035873107</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31629,28 +31753,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8111446594461436</v>
+        <v>-0.7966622409772451</v>
       </c>
       <c r="J31" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K31" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2941893882784719</v>
+        <v>0.2859816202845362</v>
       </c>
       <c r="M31" t="n">
-        <v>8.157235085195635</v>
+        <v>8.207518238909255</v>
       </c>
       <c r="N31" t="n">
-        <v>108.3636384344555</v>
+        <v>109.3684360004006</v>
       </c>
       <c r="O31" t="n">
-        <v>10.40978570550112</v>
+        <v>10.45793650776293</v>
       </c>
       <c r="P31" t="n">
-        <v>375.0039224702693</v>
+        <v>374.8745079626997</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31707,28 +31831,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6666021506071198</v>
+        <v>-0.6538941316419451</v>
       </c>
       <c r="J32" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K32" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3181607235839641</v>
+        <v>0.3082455083286549</v>
       </c>
       <c r="M32" t="n">
-        <v>6.309134040505938</v>
+        <v>6.350234985453299</v>
       </c>
       <c r="N32" t="n">
-        <v>65.53340588803442</v>
+        <v>66.38866127936713</v>
       </c>
       <c r="O32" t="n">
-        <v>8.095270587697142</v>
+        <v>8.147923740399582</v>
       </c>
       <c r="P32" t="n">
-        <v>351.721371470251</v>
+        <v>351.6078162819132</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31785,28 +31909,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4838336667573889</v>
+        <v>-0.4728102308981518</v>
       </c>
       <c r="J33" t="n">
+        <v>232</v>
+      </c>
+      <c r="K33" t="n">
         <v>231</v>
       </c>
-      <c r="K33" t="n">
-        <v>230</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.1854177587079519</v>
+        <v>0.1782206241323192</v>
       </c>
       <c r="M33" t="n">
-        <v>6.462825722570956</v>
+        <v>6.501955375571494</v>
       </c>
       <c r="N33" t="n">
-        <v>70.52824780097544</v>
+        <v>71.07564055285769</v>
       </c>
       <c r="O33" t="n">
-        <v>8.39810977547778</v>
+        <v>8.430637019398812</v>
       </c>
       <c r="P33" t="n">
-        <v>336.8232778870404</v>
+        <v>336.7249094700225</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31863,28 +31987,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5331609043805222</v>
+        <v>-0.5204711839188025</v>
       </c>
       <c r="J34" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K34" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1206504065612901</v>
+        <v>0.1158170428495232</v>
       </c>
       <c r="M34" t="n">
-        <v>9.060501057451326</v>
+        <v>9.107525839550449</v>
       </c>
       <c r="N34" t="n">
-        <v>142.6922900325203</v>
+        <v>143.2074557326958</v>
       </c>
       <c r="O34" t="n">
-        <v>11.94538781423694</v>
+        <v>11.96693175933981</v>
       </c>
       <c r="P34" t="n">
-        <v>330.6805892134276</v>
+        <v>330.5676202018043</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31941,28 +32065,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.09431233871932615</v>
+        <v>-0.08823979332233665</v>
       </c>
       <c r="J35" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K35" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002368149525134311</v>
+        <v>0.002091785508493871</v>
       </c>
       <c r="M35" t="n">
-        <v>13.01161007280307</v>
+        <v>12.98370359926235</v>
       </c>
       <c r="N35" t="n">
-        <v>258.9025597353099</v>
+        <v>258.0333369533664</v>
       </c>
       <c r="O35" t="n">
-        <v>16.09044933292137</v>
+        <v>16.06341610471964</v>
       </c>
       <c r="P35" t="n">
-        <v>305.3695220664934</v>
+        <v>305.315505384442</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -32000,7 +32124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ232"/>
+  <dimension ref="A1:AJ233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74043,6 +74167,188 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-34.5067166766269,172.70218500851018</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>-34.50593159946869,172.70229748601625</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-34.50520928572355,172.702100029031</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-34.50451101045849,172.70178384955824</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-34.5038135507167,172.7014632559279</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-34.503157066246395,172.70108609973406</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-34.50250948728453,172.70068491158685</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-34.501907865919165,172.70016143115714</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-34.501332817843014,172.69959314651427</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-34.500750779413515,172.69903663881087</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-34.500156971017034,172.69849996549448</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-34.49959209901914,172.69791450416264</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-34.49903504838358,172.69731585024803</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-34.49845771889592,172.69675137496083</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-34.49784743278989,172.69625112821348</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>-34.49722503790152,172.69577169596147</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>-34.49660426949423,172.69527831802105</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>-34.49601603358884,172.694732384227</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>-34.49546494848482,172.6941304285507</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>-34.49492806694312,172.69350705064792</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>-34.49439574779888,172.69287678738536</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>-34.49387594048911,172.69222765248531</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>-34.49335866918435,172.69162888778402</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>-34.492830177482745,172.69105734209043</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>-34.492252706769165,172.69048708759433</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>-34.49169202323818,172.6898899399156</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>-34.49117786384049,172.6892425621086</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>-34.490649111782275,172.68861093547778</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>-34.49014502092303,172.68795307795182</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>-34.489681907959856,172.6872709255407</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>-34.489226954628855,172.6865401534601</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>-34.48884581635224,172.68575880320068</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>-34.48852147115237,172.68494923153563</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>-34.488058018696506,172.6842087866097</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ233"/>
+  <dimension ref="A1:AJ234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26966,6 +26966,120 @@
       <c r="AJ233" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>375.51</v>
+      </c>
+      <c r="C234" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="D234" t="n">
+        <v>341.29</v>
+      </c>
+      <c r="E234" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="F234" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="G234" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="H234" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="I234" t="n">
+        <v>360.85</v>
+      </c>
+      <c r="J234" t="n">
+        <v>365.6</v>
+      </c>
+      <c r="K234" t="n">
+        <v>368.87</v>
+      </c>
+      <c r="L234" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="M234" t="n">
+        <v>378.21</v>
+      </c>
+      <c r="N234" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="O234" t="n">
+        <v>389.61</v>
+      </c>
+      <c r="P234" t="n">
+        <v>390.43</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>386.84</v>
+      </c>
+      <c r="R234" t="n">
+        <v>379.04</v>
+      </c>
+      <c r="S234" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="T234" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="U234" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="V234" t="n">
+        <v>390.48</v>
+      </c>
+      <c r="W234" t="n">
+        <v>401.39</v>
+      </c>
+      <c r="X234" t="n">
+        <v>408.9</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>403.21</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>379.64</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>376.31</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>369.44</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>351.08</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>330.07</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>303.81</v>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26980,7 +27094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B234"/>
+  <dimension ref="A1:B235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29323,6 +29437,16 @@
       </c>
       <c r="B234" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -29491,28 +29615,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.223383523175173</v>
+        <v>-0.2188127933056231</v>
       </c>
       <c r="J2" t="n">
+        <v>233</v>
+      </c>
+      <c r="K2" t="n">
         <v>232</v>
       </c>
-      <c r="K2" t="n">
-        <v>231</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02629344297463976</v>
+        <v>0.02546847448901068</v>
       </c>
       <c r="M2" t="n">
-        <v>8.120533323402464</v>
+        <v>8.10746169095545</v>
       </c>
       <c r="N2" t="n">
-        <v>126.8405227895133</v>
+        <v>126.4404634036458</v>
       </c>
       <c r="O2" t="n">
-        <v>11.2623497898757</v>
+        <v>11.24457484316974</v>
       </c>
       <c r="P2" t="n">
-        <v>375.6707096497304</v>
+        <v>375.6295352068443</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29569,28 +29693,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3864725766296465</v>
+        <v>-0.3906798440824121</v>
       </c>
       <c r="J3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1310850675136002</v>
+        <v>0.1344946161344822</v>
       </c>
       <c r="M3" t="n">
-        <v>6.281895626613942</v>
+        <v>6.277244117027172</v>
       </c>
       <c r="N3" t="n">
-        <v>68.10118782178688</v>
+        <v>67.93337322958639</v>
       </c>
       <c r="O3" t="n">
-        <v>8.252344383372938</v>
+        <v>8.24217041983399</v>
       </c>
       <c r="P3" t="n">
-        <v>356.8704117816224</v>
+        <v>356.908159849209</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29647,28 +29771,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3067588794709908</v>
+        <v>-0.3068712133725127</v>
       </c>
       <c r="J4" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K4" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1040508079308011</v>
+        <v>0.1050355097643616</v>
       </c>
       <c r="M4" t="n">
-        <v>6.024728295600325</v>
+        <v>5.999494405554182</v>
       </c>
       <c r="N4" t="n">
-        <v>55.73467767848118</v>
+        <v>55.49556178301625</v>
       </c>
       <c r="O4" t="n">
-        <v>7.465566132483268</v>
+        <v>7.449534333300052</v>
       </c>
       <c r="P4" t="n">
-        <v>349.721680599494</v>
+        <v>349.7226884716473</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29725,28 +29849,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2129062969328192</v>
+        <v>-0.2103082578085808</v>
       </c>
       <c r="J5" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K5" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05757415308323632</v>
+        <v>0.05672812479091205</v>
       </c>
       <c r="M5" t="n">
-        <v>5.737029075370928</v>
+        <v>5.724652270841475</v>
       </c>
       <c r="N5" t="n">
-        <v>51.03756265691314</v>
+        <v>50.86597855671249</v>
       </c>
       <c r="O5" t="n">
-        <v>7.144057856492565</v>
+        <v>7.132038877958567</v>
       </c>
       <c r="P5" t="n">
-        <v>352.5533450683675</v>
+        <v>352.5300351748189</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29803,28 +29927,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2612835279020775</v>
+        <v>-0.2540183874499093</v>
       </c>
       <c r="J6" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K6" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06379677718658439</v>
+        <v>0.06076024442709282</v>
       </c>
       <c r="M6" t="n">
-        <v>6.602707898390274</v>
+        <v>6.611068278128407</v>
       </c>
       <c r="N6" t="n">
-        <v>68.91102940345276</v>
+        <v>68.98641212598504</v>
       </c>
       <c r="O6" t="n">
-        <v>8.301266734869611</v>
+        <v>8.305805928745569</v>
       </c>
       <c r="P6" t="n">
-        <v>359.7838196357338</v>
+        <v>359.7186359943576</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29881,28 +30005,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1131106692087721</v>
+        <v>-0.1079498740029352</v>
       </c>
       <c r="J7" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K7" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007400625887487355</v>
+        <v>0.006800293181317807</v>
       </c>
       <c r="M7" t="n">
-        <v>8.754235581046213</v>
+        <v>8.743544267750528</v>
       </c>
       <c r="N7" t="n">
-        <v>118.0336869768487</v>
+        <v>117.7143800988213</v>
       </c>
       <c r="O7" t="n">
-        <v>10.86433094934284</v>
+        <v>10.84962580455295</v>
       </c>
       <c r="P7" t="n">
-        <v>369.8897925876529</v>
+        <v>369.8434893639055</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29959,28 +30083,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.149637189422225</v>
+        <v>-0.1490001176349442</v>
       </c>
       <c r="J8" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K8" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0189397671688154</v>
+        <v>0.01896243412457566</v>
       </c>
       <c r="M8" t="n">
-        <v>7.344002322992329</v>
+        <v>7.316391154413985</v>
       </c>
       <c r="N8" t="n">
-        <v>79.7798846527359</v>
+        <v>79.44033551993441</v>
       </c>
       <c r="O8" t="n">
-        <v>8.931958612350144</v>
+        <v>8.912930804170669</v>
       </c>
       <c r="P8" t="n">
-        <v>366.6159246630658</v>
+        <v>366.6102087847306</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30037,28 +30161,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3762226061873021</v>
+        <v>-0.3727851011403135</v>
       </c>
       <c r="J9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06608501612493756</v>
+        <v>0.06552094954727694</v>
       </c>
       <c r="M9" t="n">
-        <v>9.476358104477203</v>
+        <v>9.454415397078655</v>
       </c>
       <c r="N9" t="n">
-        <v>137.5901680917279</v>
+        <v>137.0827395888143</v>
       </c>
       <c r="O9" t="n">
-        <v>11.729883549794</v>
+        <v>11.70823383729648</v>
       </c>
       <c r="P9" t="n">
-        <v>366.5772992018211</v>
+        <v>366.5464575274326</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30115,28 +30239,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5123528069143043</v>
+        <v>-0.5092362026999296</v>
       </c>
       <c r="J10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1354305526131598</v>
+        <v>0.1350785332347697</v>
       </c>
       <c r="M10" t="n">
-        <v>9.005841704276797</v>
+        <v>8.983668100002772</v>
       </c>
       <c r="N10" t="n">
-        <v>115.2695920796394</v>
+        <v>114.8431712665522</v>
       </c>
       <c r="O10" t="n">
-        <v>10.73636773213545</v>
+        <v>10.71649062270631</v>
       </c>
       <c r="P10" t="n">
-        <v>375.4153022909948</v>
+        <v>375.3873397742672</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30193,28 +30317,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6084451527595608</v>
+        <v>-0.6045248549816371</v>
       </c>
       <c r="J11" t="n">
+        <v>233</v>
+      </c>
+      <c r="K11" t="n">
         <v>232</v>
       </c>
-      <c r="K11" t="n">
-        <v>231</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1744400939342989</v>
+        <v>0.1738578894990029</v>
       </c>
       <c r="M11" t="n">
-        <v>8.942427004631195</v>
+        <v>8.924211388912257</v>
       </c>
       <c r="N11" t="n">
-        <v>121.024605361607</v>
+        <v>120.6115508226215</v>
       </c>
       <c r="O11" t="n">
-        <v>11.00111836867539</v>
+        <v>10.98232902542177</v>
       </c>
       <c r="P11" t="n">
-        <v>380.2426964358171</v>
+        <v>380.2076024010719</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30271,28 +30395,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6618594419880625</v>
+        <v>-0.6580418473574903</v>
       </c>
       <c r="J12" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K12" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1717146104632761</v>
+        <v>0.1713553778029316</v>
       </c>
       <c r="M12" t="n">
-        <v>9.619369532337139</v>
+        <v>9.596513508499351</v>
       </c>
       <c r="N12" t="n">
-        <v>145.8399662030539</v>
+        <v>145.3118268431235</v>
       </c>
       <c r="O12" t="n">
-        <v>12.07642191226581</v>
+        <v>12.0545355299623</v>
       </c>
       <c r="P12" t="n">
-        <v>382.5611626491728</v>
+        <v>382.5268624059996</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30349,28 +30473,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8743827792145829</v>
+        <v>-0.8644609810147384</v>
       </c>
       <c r="J13" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K13" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L13" t="n">
-        <v>0.251017600395775</v>
+        <v>0.2477350377907447</v>
       </c>
       <c r="M13" t="n">
-        <v>10.26352352661032</v>
+        <v>10.26809822362875</v>
       </c>
       <c r="N13" t="n">
-        <v>157.8317714008642</v>
+        <v>157.8456674837076</v>
       </c>
       <c r="O13" t="n">
-        <v>12.5631115334086</v>
+        <v>12.56366457223797</v>
       </c>
       <c r="P13" t="n">
-        <v>389.0403286872937</v>
+        <v>388.9511830643024</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30427,28 +30551,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8164687598985015</v>
+        <v>-0.8050727518425514</v>
       </c>
       <c r="J14" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K14" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2857539449003276</v>
+        <v>0.2803976332101303</v>
       </c>
       <c r="M14" t="n">
-        <v>8.58538294103931</v>
+        <v>8.605569383240733</v>
       </c>
       <c r="N14" t="n">
-        <v>115.2812192052211</v>
+        <v>115.7036262978114</v>
       </c>
       <c r="O14" t="n">
-        <v>10.73690920168468</v>
+        <v>10.7565620110615</v>
       </c>
       <c r="P14" t="n">
-        <v>393.0014937847213</v>
+        <v>392.899102643791</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30505,28 +30629,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9527969482189856</v>
+        <v>-0.9393074082153221</v>
       </c>
       <c r="J15" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K15" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3366337923069126</v>
+        <v>0.3301541139870152</v>
       </c>
       <c r="M15" t="n">
-        <v>8.910118973439197</v>
+        <v>8.943700925330148</v>
       </c>
       <c r="N15" t="n">
-        <v>122.8686165564189</v>
+        <v>123.6072040330317</v>
       </c>
       <c r="O15" t="n">
-        <v>11.08461170075068</v>
+        <v>11.11787767665357</v>
       </c>
       <c r="P15" t="n">
-        <v>398.1791881116516</v>
+        <v>398.0566654844685</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30583,28 +30707,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8828672329856957</v>
+        <v>-0.8726901059127401</v>
       </c>
       <c r="J16" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K16" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3188628986252598</v>
+        <v>0.3145787111686498</v>
       </c>
       <c r="M16" t="n">
-        <v>8.73117634178638</v>
+        <v>8.748998465793694</v>
       </c>
       <c r="N16" t="n">
-        <v>114.3578450150922</v>
+        <v>114.5825469328105</v>
       </c>
       <c r="O16" t="n">
-        <v>10.69382275031208</v>
+        <v>10.70432374943931</v>
       </c>
       <c r="P16" t="n">
-        <v>401.3258869061128</v>
+        <v>401.2334502221475</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30661,28 +30785,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9100986233473637</v>
+        <v>-0.9046177421282162</v>
       </c>
       <c r="J17" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K17" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3614705624276671</v>
+        <v>0.3604429315511722</v>
       </c>
       <c r="M17" t="n">
-        <v>8.065481799425591</v>
+        <v>8.060701283596849</v>
       </c>
       <c r="N17" t="n">
-        <v>100.8230635378092</v>
+        <v>100.5953860199006</v>
       </c>
       <c r="O17" t="n">
-        <v>10.04106884439148</v>
+        <v>10.02972512185158</v>
       </c>
       <c r="P17" t="n">
-        <v>404.3913837750529</v>
+        <v>404.3418745368355</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30739,28 +30863,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.028290465447846</v>
+        <v>-1.028721117159801</v>
       </c>
       <c r="J18" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K18" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L18" t="n">
-        <v>0.400512408877291</v>
+        <v>0.4030521997393171</v>
       </c>
       <c r="M18" t="n">
-        <v>8.405121812170455</v>
+        <v>8.370544092240479</v>
       </c>
       <c r="N18" t="n">
-        <v>109.0613389408262</v>
+        <v>108.5864010861958</v>
       </c>
       <c r="O18" t="n">
-        <v>10.44324369823984</v>
+        <v>10.42047988751938</v>
       </c>
       <c r="P18" t="n">
-        <v>407.3583035906819</v>
+        <v>407.3621937020241</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30817,28 +30941,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.069311410918379</v>
+        <v>-1.073076722969172</v>
       </c>
       <c r="J19" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K19" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4254595321538153</v>
+        <v>0.4293421468720877</v>
       </c>
       <c r="M19" t="n">
-        <v>8.45242949497484</v>
+        <v>8.436652192609557</v>
       </c>
       <c r="N19" t="n">
-        <v>105.7380753395686</v>
+        <v>105.3796799204285</v>
       </c>
       <c r="O19" t="n">
-        <v>10.28290208742496</v>
+        <v>10.26546053133655</v>
       </c>
       <c r="P19" t="n">
-        <v>408.3064108479409</v>
+        <v>408.3404721692962</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30895,28 +31019,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9572328248383282</v>
+        <v>-0.9605844141884535</v>
       </c>
       <c r="J20" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K20" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3101324270444001</v>
+        <v>0.3136118273750457</v>
       </c>
       <c r="M20" t="n">
-        <v>9.71500922842783</v>
+        <v>9.693975937157262</v>
       </c>
       <c r="N20" t="n">
-        <v>140.1996734914686</v>
+        <v>139.6769439956901</v>
       </c>
       <c r="O20" t="n">
-        <v>11.84059430482561</v>
+        <v>11.81850007385413</v>
       </c>
       <c r="P20" t="n">
-        <v>406.3714642888398</v>
+        <v>406.4015351181207</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30973,28 +31097,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.307466282552553</v>
+        <v>-1.305583693711832</v>
       </c>
       <c r="J21" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K21" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4824714138396711</v>
+        <v>0.4841465262077168</v>
       </c>
       <c r="M21" t="n">
-        <v>9.28369650224897</v>
+        <v>9.255143515721668</v>
       </c>
       <c r="N21" t="n">
-        <v>126.1296049879353</v>
+        <v>125.6131968174362</v>
       </c>
       <c r="O21" t="n">
-        <v>11.23074374153089</v>
+        <v>11.20772933369807</v>
       </c>
       <c r="P21" t="n">
-        <v>414.7729404045118</v>
+        <v>414.7560496098106</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31051,28 +31175,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.361942770013224</v>
+        <v>-1.355040945873681</v>
       </c>
       <c r="J22" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K22" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5688300829184898</v>
+        <v>0.5678867703657191</v>
       </c>
       <c r="M22" t="n">
-        <v>8.195293059526756</v>
+        <v>8.202600352614448</v>
       </c>
       <c r="N22" t="n">
-        <v>96.71122763741116</v>
+        <v>96.63110447388317</v>
       </c>
       <c r="O22" t="n">
-        <v>9.834186678999497</v>
+        <v>9.830112129262981</v>
       </c>
       <c r="P22" t="n">
-        <v>418.3662230991189</v>
+        <v>418.3042991717681</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31129,28 +31253,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.120776972872663</v>
+        <v>-1.109283704809275</v>
       </c>
       <c r="J23" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K23" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5032923315184231</v>
+        <v>0.4978656167781713</v>
       </c>
       <c r="M23" t="n">
-        <v>7.634072084035289</v>
+        <v>7.670732843251709</v>
       </c>
       <c r="N23" t="n">
-        <v>85.27313577715606</v>
+        <v>85.83598340654862</v>
       </c>
       <c r="O23" t="n">
-        <v>9.234345443893469</v>
+        <v>9.264771093046424</v>
       </c>
       <c r="P23" t="n">
-        <v>416.8467765341269</v>
+        <v>416.7436576655219</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31207,28 +31331,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.101814145976014</v>
+        <v>-1.086147090619975</v>
       </c>
       <c r="J24" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K24" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4357660648064857</v>
+        <v>0.4272396310304506</v>
       </c>
       <c r="M24" t="n">
-        <v>8.474292593297209</v>
+        <v>8.528969857196484</v>
       </c>
       <c r="N24" t="n">
-        <v>108.1224223448935</v>
+        <v>109.3843045211379</v>
       </c>
       <c r="O24" t="n">
-        <v>10.39819322502201</v>
+        <v>10.4586951634101</v>
       </c>
       <c r="P24" t="n">
-        <v>418.4565486675746</v>
+        <v>418.3159821190719</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31285,28 +31409,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.332513470701209</v>
+        <v>-1.314694039323607</v>
       </c>
       <c r="J25" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K25" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5376841158576152</v>
+        <v>0.5281594081545717</v>
       </c>
       <c r="M25" t="n">
-        <v>8.20447657912788</v>
+        <v>8.282523441418155</v>
       </c>
       <c r="N25" t="n">
-        <v>105.0142191649308</v>
+        <v>106.7962398314574</v>
       </c>
       <c r="O25" t="n">
-        <v>10.24764456667632</v>
+        <v>10.33422661990037</v>
       </c>
       <c r="P25" t="n">
-        <v>416.2243858216176</v>
+        <v>416.0645079180735</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31363,28 +31487,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.360143630577822</v>
+        <v>-1.344617620084843</v>
       </c>
       <c r="J26" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K26" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4978132196456795</v>
+        <v>0.4912273925069882</v>
       </c>
       <c r="M26" t="n">
-        <v>9.19681128293052</v>
+        <v>9.257158279895917</v>
       </c>
       <c r="N26" t="n">
-        <v>128.3694492815818</v>
+        <v>129.5134984305553</v>
       </c>
       <c r="O26" t="n">
-        <v>11.33002424011449</v>
+        <v>11.38039974827578</v>
       </c>
       <c r="P26" t="n">
-        <v>406.7428464098721</v>
+        <v>406.6035453314358</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31441,28 +31565,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.052338078898136</v>
+        <v>-1.04064439170978</v>
       </c>
       <c r="J27" t="n">
+        <v>233</v>
+      </c>
+      <c r="K27" t="n">
         <v>232</v>
       </c>
-      <c r="K27" t="n">
-        <v>231</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.4047697097114393</v>
+        <v>0.399677719029496</v>
       </c>
       <c r="M27" t="n">
-        <v>8.477493785894207</v>
+        <v>8.512644044828772</v>
       </c>
       <c r="N27" t="n">
-        <v>112.3486396878341</v>
+        <v>112.8304992999164</v>
       </c>
       <c r="O27" t="n">
-        <v>10.59946412267309</v>
+        <v>10.6221701784483</v>
       </c>
       <c r="P27" t="n">
-        <v>392.9824596245744</v>
+        <v>392.8776007403844</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31519,28 +31643,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9705167068173494</v>
+        <v>-0.9576652536061482</v>
       </c>
       <c r="J28" t="n">
+        <v>233</v>
+      </c>
+      <c r="K28" t="n">
         <v>232</v>
       </c>
-      <c r="K28" t="n">
-        <v>231</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.382095811695816</v>
+        <v>0.3755115852718339</v>
       </c>
       <c r="M28" t="n">
-        <v>8.150517002216892</v>
+        <v>8.193777203473912</v>
       </c>
       <c r="N28" t="n">
-        <v>105.0836434707687</v>
+        <v>105.797595153322</v>
       </c>
       <c r="O28" t="n">
-        <v>10.25103133693233</v>
+        <v>10.28579579582066</v>
       </c>
       <c r="P28" t="n">
-        <v>385.9460232695816</v>
+        <v>385.8307825399264</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31597,28 +31721,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9271797124561098</v>
+        <v>-0.9135371025782348</v>
       </c>
       <c r="J29" t="n">
+        <v>233</v>
+      </c>
+      <c r="K29" t="n">
         <v>232</v>
       </c>
-      <c r="K29" t="n">
-        <v>231</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.3304412040260827</v>
+        <v>0.3236611464988343</v>
       </c>
       <c r="M29" t="n">
-        <v>8.391903281683266</v>
+        <v>8.433153883783818</v>
       </c>
       <c r="N29" t="n">
-        <v>120.171807425242</v>
+        <v>120.9688186577014</v>
       </c>
       <c r="O29" t="n">
-        <v>10.96229024543877</v>
+        <v>10.99858257493671</v>
       </c>
       <c r="P29" t="n">
-        <v>378.8535866804517</v>
+        <v>378.7312515413129</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31675,28 +31799,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7829320246814269</v>
+        <v>-0.7696450918066149</v>
       </c>
       <c r="J30" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K30" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2602848670735558</v>
+        <v>0.2536416264275722</v>
       </c>
       <c r="M30" t="n">
-        <v>8.283996950479015</v>
+        <v>8.320438812900322</v>
       </c>
       <c r="N30" t="n">
-        <v>119.827633581967</v>
+        <v>120.5547101162388</v>
       </c>
       <c r="O30" t="n">
-        <v>10.94658090830041</v>
+        <v>10.97974089476791</v>
       </c>
       <c r="P30" t="n">
-        <v>373.4548035873107</v>
+        <v>373.3355917602024</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31753,28 +31877,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7966622409772451</v>
+        <v>-0.7822103293295207</v>
       </c>
       <c r="J31" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K31" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2859816202845362</v>
+        <v>0.2778134379446476</v>
       </c>
       <c r="M31" t="n">
-        <v>8.207518238909255</v>
+        <v>8.262317624348388</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3684360004006</v>
+        <v>110.3739555741692</v>
       </c>
       <c r="O31" t="n">
-        <v>10.45793650776293</v>
+        <v>10.50590098821463</v>
       </c>
       <c r="P31" t="n">
-        <v>374.8745079626997</v>
+        <v>374.7446607338015</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31831,28 +31955,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6538941316419451</v>
+        <v>-0.6405966183803055</v>
       </c>
       <c r="J32" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K32" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3082455083286549</v>
+        <v>0.2976446712966286</v>
       </c>
       <c r="M32" t="n">
-        <v>6.350234985453299</v>
+        <v>6.398381744732168</v>
       </c>
       <c r="N32" t="n">
-        <v>66.38866127936713</v>
+        <v>67.35758819804505</v>
       </c>
       <c r="O32" t="n">
-        <v>8.147923740399582</v>
+        <v>8.207166880114297</v>
       </c>
       <c r="P32" t="n">
-        <v>351.6078162819132</v>
+        <v>351.488340448998</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31909,28 +32033,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4728102308981518</v>
+        <v>-0.4622286998644791</v>
       </c>
       <c r="J33" t="n">
+        <v>233</v>
+      </c>
+      <c r="K33" t="n">
         <v>232</v>
       </c>
-      <c r="K33" t="n">
-        <v>231</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.1782206241323192</v>
+        <v>0.1714962746419233</v>
       </c>
       <c r="M33" t="n">
-        <v>6.501955375571494</v>
+        <v>6.539347616523314</v>
       </c>
       <c r="N33" t="n">
-        <v>71.07564055285769</v>
+        <v>71.55998449456744</v>
       </c>
       <c r="O33" t="n">
-        <v>8.430637019398812</v>
+        <v>8.459313476551596</v>
       </c>
       <c r="P33" t="n">
-        <v>336.7249094700225</v>
+        <v>336.6299711560289</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31987,28 +32111,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5204711839188025</v>
+        <v>-0.5099593079067931</v>
       </c>
       <c r="J34" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K34" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1158170428495232</v>
+        <v>0.1121285316933427</v>
       </c>
       <c r="M34" t="n">
-        <v>9.107525839550449</v>
+        <v>9.138906455313714</v>
       </c>
       <c r="N34" t="n">
-        <v>143.2074557326958</v>
+        <v>143.3716951663004</v>
       </c>
       <c r="O34" t="n">
-        <v>11.96693175933981</v>
+        <v>11.97379201282118</v>
       </c>
       <c r="P34" t="n">
-        <v>330.5676202018043</v>
+        <v>330.4735267907109</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -32065,28 +32189,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.08823979332233665</v>
+        <v>-0.08755636709239126</v>
       </c>
       <c r="J35" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K35" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002091785508493871</v>
+        <v>0.002079674728723946</v>
       </c>
       <c r="M35" t="n">
-        <v>12.98370359926235</v>
+        <v>12.93045957444393</v>
       </c>
       <c r="N35" t="n">
-        <v>258.0333369533664</v>
+        <v>256.9147841106076</v>
       </c>
       <c r="O35" t="n">
-        <v>16.06341610471964</v>
+        <v>16.02856151095935</v>
       </c>
       <c r="P35" t="n">
-        <v>305.315505384442</v>
+        <v>305.3093926272084</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -32124,7 +32248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ233"/>
+  <dimension ref="A1:AJ234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74349,6 +74473,188 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>-34.506712690600324,172.70220469024443</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>-34.50592009132439,172.70235430852387</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-34.505202020842546,172.70213589992505</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-34.504502331256845,172.7018267038318</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-34.503808951448185,172.7014847725088</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-34.50313855000618,172.70113312068875</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-34.50249766906522,172.70070483458542</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-34.50188365180786,172.7002022509639</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-34.50130797355823,172.6996350286991</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-34.50072451708754,172.69908091153914</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-34.500127714923714,172.69854928508244</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-34.49957229742839,172.69794788551457</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-34.49901062480666,172.6973570233757</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-34.498430879360285,172.69679662093492</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>-34.497837758124604,172.69626687185067</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>-34.49723728584514,172.695752844167</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>-34.496618364716944,172.69525706528785</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>-34.49601676653746,172.69473127908984</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>-34.49544921835461,172.694154146408</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>-34.49490472557834,172.69354224477527</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>-34.49437657866344,172.6929056906897</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>-34.49386150733752,172.69224941491575</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>-34.493348054360474,172.69164284529043</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>-34.49282666320942,172.69106125468036</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>-34.49224974841381,172.69049028141492</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>-34.49168805636488,172.68989422252662</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>-34.49117376251151,172.6892469898855</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>-34.490648842843605,172.68861122582325</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>-34.490143940016615,172.68795423232854</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>-34.489683671452305,172.68726960681965</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>-34.48923537779493,172.68653596784472</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>-34.488842980836516,172.68576021222947</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>-34.48850020482838,172.68495979933806</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>-34.4880012252005,172.68423700898964</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ234"/>
+  <dimension ref="A1:AJ235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27080,6 +27080,120 @@
       <c r="AJ234" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>372.65</v>
+      </c>
+      <c r="C235" t="n">
+        <v>337.77</v>
+      </c>
+      <c r="D235" t="n">
+        <v>338.9</v>
+      </c>
+      <c r="E235" t="n">
+        <v>346.47</v>
+      </c>
+      <c r="F235" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="G235" t="n">
+        <v>369.17</v>
+      </c>
+      <c r="H235" t="n">
+        <v>360.96</v>
+      </c>
+      <c r="I235" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="J235" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="K235" t="n">
+        <v>367.88</v>
+      </c>
+      <c r="L235" t="n">
+        <v>368.27</v>
+      </c>
+      <c r="M235" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="N235" t="n">
+        <v>381.95</v>
+      </c>
+      <c r="O235" t="n">
+        <v>385.48</v>
+      </c>
+      <c r="P235" t="n">
+        <v>387.57</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>384.14</v>
+      </c>
+      <c r="R235" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="S235" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="T235" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="U235" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="V235" t="n">
+        <v>389.59</v>
+      </c>
+      <c r="W235" t="n">
+        <v>398.43</v>
+      </c>
+      <c r="X235" t="n">
+        <v>406.1</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>399.86</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>388.29</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>378.49</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>375.42</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>371</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>370.85</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>348.68</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>302.41</v>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B235"/>
+  <dimension ref="A1:B236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29447,6 +29561,16 @@
       </c>
       <c r="B235" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
@@ -29615,28 +29739,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2188127933056231</v>
+        <v>-0.216528369316065</v>
       </c>
       <c r="J2" t="n">
+        <v>234</v>
+      </c>
+      <c r="K2" t="n">
         <v>233</v>
       </c>
-      <c r="K2" t="n">
-        <v>232</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02546847448901068</v>
+        <v>0.02518438365185838</v>
       </c>
       <c r="M2" t="n">
-        <v>8.10746169095545</v>
+        <v>8.083696466946163</v>
       </c>
       <c r="N2" t="n">
-        <v>126.4404634036458</v>
+        <v>125.9346712250472</v>
       </c>
       <c r="O2" t="n">
-        <v>11.24457484316974</v>
+        <v>11.22206180811027</v>
       </c>
       <c r="P2" t="n">
-        <v>375.6295352068443</v>
+        <v>375.608846181985</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29693,28 +29817,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3906798440824121</v>
+        <v>-0.397274826420579</v>
       </c>
       <c r="J3" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K3" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1344946161344822</v>
+        <v>0.1390658427216375</v>
       </c>
       <c r="M3" t="n">
-        <v>6.277244117027172</v>
+        <v>6.286178880972022</v>
       </c>
       <c r="N3" t="n">
-        <v>67.93337322958639</v>
+        <v>67.95085725497795</v>
       </c>
       <c r="O3" t="n">
-        <v>8.24217041983399</v>
+        <v>8.243230996094793</v>
       </c>
       <c r="P3" t="n">
-        <v>356.908159849209</v>
+        <v>356.9676475907123</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29771,28 +29895,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3068712133725127</v>
+        <v>-0.3088000793997221</v>
       </c>
       <c r="J4" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K4" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1050355097643616</v>
+        <v>0.107105800155465</v>
       </c>
       <c r="M4" t="n">
-        <v>5.999494405554182</v>
+        <v>5.984417559378137</v>
       </c>
       <c r="N4" t="n">
-        <v>55.49556178301625</v>
+        <v>55.2847307293649</v>
       </c>
       <c r="O4" t="n">
-        <v>7.449534333300052</v>
+        <v>7.435370248304041</v>
       </c>
       <c r="P4" t="n">
-        <v>349.7226884716473</v>
+        <v>349.7400871359253</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29849,28 +29973,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2103082578085808</v>
+        <v>-0.2105809468624266</v>
       </c>
       <c r="J5" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K5" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05672812479091205</v>
+        <v>0.05739315981636761</v>
       </c>
       <c r="M5" t="n">
-        <v>5.724652270841475</v>
+        <v>5.70189172375012</v>
       </c>
       <c r="N5" t="n">
-        <v>50.86597855671249</v>
+        <v>50.64912880723951</v>
       </c>
       <c r="O5" t="n">
-        <v>7.132038877958567</v>
+        <v>7.116820133124028</v>
       </c>
       <c r="P5" t="n">
-        <v>352.5300351748189</v>
+        <v>352.5324948714662</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29927,28 +30051,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2540183874499093</v>
+        <v>-0.2505635280999194</v>
       </c>
       <c r="J6" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K6" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06076024442709282</v>
+        <v>0.05969403572884768</v>
       </c>
       <c r="M6" t="n">
-        <v>6.611068278128407</v>
+        <v>6.600058917585873</v>
       </c>
       <c r="N6" t="n">
-        <v>68.98641212598504</v>
+        <v>68.77606765695904</v>
       </c>
       <c r="O6" t="n">
-        <v>8.305805928745569</v>
+        <v>8.293133765770273</v>
       </c>
       <c r="P6" t="n">
-        <v>359.7186359943576</v>
+        <v>359.6874726387329</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30005,28 +30129,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1079498740029352</v>
+        <v>-0.1062093090698121</v>
       </c>
       <c r="J7" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K7" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006800293181317807</v>
+        <v>0.006647265477629061</v>
       </c>
       <c r="M7" t="n">
-        <v>8.743544267750528</v>
+        <v>8.715130812749598</v>
       </c>
       <c r="N7" t="n">
-        <v>117.7143800988213</v>
+        <v>117.2327668771721</v>
       </c>
       <c r="O7" t="n">
-        <v>10.84962580455295</v>
+        <v>10.82740813293616</v>
       </c>
       <c r="P7" t="n">
-        <v>369.8434893639055</v>
+        <v>369.8277892040715</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30083,28 +30207,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1490001176349442</v>
+        <v>-0.1502398768242859</v>
       </c>
       <c r="J8" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K8" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01896243412457566</v>
+        <v>0.01945628545031353</v>
       </c>
       <c r="M8" t="n">
-        <v>7.316391154413985</v>
+        <v>7.291152422941679</v>
       </c>
       <c r="N8" t="n">
-        <v>79.44033551993441</v>
+        <v>79.11172399375027</v>
       </c>
       <c r="O8" t="n">
-        <v>8.912930804170669</v>
+        <v>8.894477162472805</v>
       </c>
       <c r="P8" t="n">
-        <v>366.6102087847306</v>
+        <v>366.6213916007566</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30161,28 +30285,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3727851011403135</v>
+        <v>-0.3710345941019857</v>
       </c>
       <c r="J9" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K9" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06552094954727694</v>
+        <v>0.06553360313493828</v>
       </c>
       <c r="M9" t="n">
-        <v>9.454415397078655</v>
+        <v>9.423548208124174</v>
       </c>
       <c r="N9" t="n">
-        <v>137.0827395888143</v>
+        <v>136.5186012265419</v>
       </c>
       <c r="O9" t="n">
-        <v>11.70823383729648</v>
+        <v>11.68411747743671</v>
       </c>
       <c r="P9" t="n">
-        <v>366.5464575274326</v>
+        <v>366.5306676883009</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30239,28 +30363,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5092362026999296</v>
+        <v>-0.5074169561415496</v>
       </c>
       <c r="J10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1350785332347697</v>
+        <v>0.1353611116672904</v>
       </c>
       <c r="M10" t="n">
-        <v>8.983668100002772</v>
+        <v>8.954840447716588</v>
       </c>
       <c r="N10" t="n">
-        <v>114.8431712665522</v>
+        <v>114.3758103260691</v>
       </c>
       <c r="O10" t="n">
-        <v>10.71649062270631</v>
+        <v>10.69466270277231</v>
       </c>
       <c r="P10" t="n">
-        <v>375.3873397742672</v>
+        <v>375.3709298942333</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30317,28 +30441,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6045248549816371</v>
+        <v>-0.601393431268107</v>
       </c>
       <c r="J11" t="n">
+        <v>234</v>
+      </c>
+      <c r="K11" t="n">
         <v>233</v>
       </c>
-      <c r="K11" t="n">
-        <v>232</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1738578894990029</v>
+        <v>0.1736861796310197</v>
       </c>
       <c r="M11" t="n">
-        <v>8.924211388912257</v>
+        <v>8.901938683935207</v>
       </c>
       <c r="N11" t="n">
-        <v>120.6115508226215</v>
+        <v>120.1636438590517</v>
       </c>
       <c r="O11" t="n">
-        <v>10.98232902542177</v>
+        <v>10.9619178914573</v>
       </c>
       <c r="P11" t="n">
-        <v>380.2076024010719</v>
+        <v>380.1794190685147</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30395,28 +30519,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6580418473574903</v>
+        <v>-0.6552734301680082</v>
       </c>
       <c r="J12" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K12" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1713553778029316</v>
+        <v>0.1714880566129526</v>
       </c>
       <c r="M12" t="n">
-        <v>9.596513508499351</v>
+        <v>9.568594247161819</v>
       </c>
       <c r="N12" t="n">
-        <v>145.3118268431235</v>
+        <v>144.740098123601</v>
       </c>
       <c r="O12" t="n">
-        <v>12.0545355299623</v>
+        <v>12.03079790053848</v>
       </c>
       <c r="P12" t="n">
-        <v>382.5268624059996</v>
+        <v>382.5018541447686</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30473,28 +30597,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8644609810147384</v>
+        <v>-0.8580656384826972</v>
       </c>
       <c r="J13" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K13" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2477350377907447</v>
+        <v>0.2464351754275131</v>
       </c>
       <c r="M13" t="n">
-        <v>10.26809822362875</v>
+        <v>10.254946139613</v>
       </c>
       <c r="N13" t="n">
-        <v>157.8456674837076</v>
+        <v>157.4550634162336</v>
       </c>
       <c r="O13" t="n">
-        <v>12.56366457223797</v>
+        <v>12.54810995394261</v>
       </c>
       <c r="P13" t="n">
-        <v>388.9511830643024</v>
+        <v>388.8934090274325</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30551,28 +30675,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8050727518425514</v>
+        <v>-0.7966719610447477</v>
       </c>
       <c r="J14" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K14" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2803976332101303</v>
+        <v>0.2772548955449241</v>
       </c>
       <c r="M14" t="n">
-        <v>8.605569383240733</v>
+        <v>8.610170476023034</v>
       </c>
       <c r="N14" t="n">
-        <v>115.7036262978114</v>
+        <v>115.707814174302</v>
       </c>
       <c r="O14" t="n">
-        <v>10.7565620110615</v>
+        <v>10.75675667542508</v>
       </c>
       <c r="P14" t="n">
-        <v>392.899102643791</v>
+        <v>392.823211853758</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30629,28 +30753,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9393074082153221</v>
+        <v>-0.9292253052012256</v>
       </c>
       <c r="J15" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K15" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3301541139870152</v>
+        <v>0.3262623613696951</v>
       </c>
       <c r="M15" t="n">
-        <v>8.943700925330148</v>
+        <v>8.958325032954907</v>
       </c>
       <c r="N15" t="n">
-        <v>123.6072040330317</v>
+        <v>123.7844848568172</v>
       </c>
       <c r="O15" t="n">
-        <v>11.11787767665357</v>
+        <v>11.12584760172533</v>
       </c>
       <c r="P15" t="n">
-        <v>398.0566654844685</v>
+        <v>397.9645937927004</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30707,28 +30831,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8726901059127401</v>
+        <v>-0.8648759885530839</v>
       </c>
       <c r="J16" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K16" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3145787111686498</v>
+        <v>0.3119952019977257</v>
       </c>
       <c r="M16" t="n">
-        <v>8.748998465793694</v>
+        <v>8.753914980872565</v>
       </c>
       <c r="N16" t="n">
-        <v>114.5825469328105</v>
+        <v>114.5121460712234</v>
       </c>
       <c r="O16" t="n">
-        <v>10.70432374943931</v>
+        <v>10.70103481310211</v>
       </c>
       <c r="P16" t="n">
-        <v>401.2334502221475</v>
+        <v>401.1620902088673</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30785,28 +30909,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9046177421282162</v>
+        <v>-0.9012562838721635</v>
       </c>
       <c r="J17" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K17" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3604429315511722</v>
+        <v>0.3607852437558391</v>
       </c>
       <c r="M17" t="n">
-        <v>8.060701283596849</v>
+        <v>8.044073186419505</v>
       </c>
       <c r="N17" t="n">
-        <v>100.5953860199006</v>
+        <v>100.2384819753853</v>
       </c>
       <c r="O17" t="n">
-        <v>10.02972512185158</v>
+        <v>10.01191699802717</v>
       </c>
       <c r="P17" t="n">
-        <v>404.3418745368355</v>
+        <v>404.3113451260345</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30863,28 +30987,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.028721117159801</v>
+        <v>-1.029706014502509</v>
       </c>
       <c r="J18" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K18" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4030521997393171</v>
+        <v>0.4058422600766929</v>
       </c>
       <c r="M18" t="n">
-        <v>8.370544092240479</v>
+        <v>8.338942759494577</v>
       </c>
       <c r="N18" t="n">
-        <v>108.5864010861958</v>
+        <v>108.1211941881924</v>
       </c>
       <c r="O18" t="n">
-        <v>10.42047988751938</v>
+        <v>10.39813416859931</v>
       </c>
       <c r="P18" t="n">
-        <v>407.3621937020241</v>
+        <v>407.3711387292361</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30941,28 +31065,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.073076722969172</v>
+        <v>-1.075165031221274</v>
       </c>
       <c r="J19" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K19" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4293421468720877</v>
+        <v>0.4326197133486497</v>
       </c>
       <c r="M19" t="n">
-        <v>8.436652192609557</v>
+        <v>8.411840199268626</v>
       </c>
       <c r="N19" t="n">
-        <v>105.3796799204285</v>
+        <v>104.9562095124842</v>
       </c>
       <c r="O19" t="n">
-        <v>10.26546053133655</v>
+        <v>10.24481378613024</v>
       </c>
       <c r="P19" t="n">
-        <v>408.3404721692962</v>
+        <v>408.3594644723788</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31019,28 +31143,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9605844141884535</v>
+        <v>-0.9625904238457037</v>
       </c>
       <c r="J20" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K20" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3136118273750457</v>
+        <v>0.3165784851955312</v>
       </c>
       <c r="M20" t="n">
-        <v>9.693975937157262</v>
+        <v>9.664760440465058</v>
       </c>
       <c r="N20" t="n">
-        <v>139.6769439956901</v>
+        <v>139.1085116172632</v>
       </c>
       <c r="O20" t="n">
-        <v>11.81850007385413</v>
+        <v>11.79442714239497</v>
       </c>
       <c r="P20" t="n">
-        <v>406.4015351181207</v>
+        <v>406.4196296296485</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31097,28 +31221,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.305583693711832</v>
+        <v>-1.302941517819776</v>
       </c>
       <c r="J21" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K21" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4841465262077168</v>
+        <v>0.485478449187928</v>
       </c>
       <c r="M21" t="n">
-        <v>9.255143515721668</v>
+        <v>9.231249369022303</v>
       </c>
       <c r="N21" t="n">
-        <v>125.6131968174362</v>
+        <v>125.1257922014719</v>
       </c>
       <c r="O21" t="n">
-        <v>11.20772933369807</v>
+        <v>11.18596407116847</v>
       </c>
       <c r="P21" t="n">
-        <v>414.7560496098106</v>
+        <v>414.7322167823044</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31175,28 +31299,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.355040945873681</v>
+        <v>-1.348841867807535</v>
       </c>
       <c r="J22" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K22" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5678867703657191</v>
+        <v>0.5673434069216212</v>
       </c>
       <c r="M22" t="n">
-        <v>8.202600352614448</v>
+        <v>8.205660374743763</v>
       </c>
       <c r="N22" t="n">
-        <v>96.63110447388317</v>
+        <v>96.49010296713152</v>
       </c>
       <c r="O22" t="n">
-        <v>9.830112129262981</v>
+        <v>9.822937593568001</v>
       </c>
       <c r="P22" t="n">
-        <v>418.3042991717681</v>
+        <v>418.2483825468784</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31253,28 +31377,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.109283704809275</v>
+        <v>-1.100206298755697</v>
       </c>
       <c r="J23" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K23" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4978656167781713</v>
+        <v>0.4945023469935796</v>
       </c>
       <c r="M23" t="n">
-        <v>7.670732843251709</v>
+        <v>7.69206880656288</v>
       </c>
       <c r="N23" t="n">
-        <v>85.83598340654862</v>
+        <v>86.0522876971212</v>
       </c>
       <c r="O23" t="n">
-        <v>9.264771093046424</v>
+        <v>9.276437230808021</v>
       </c>
       <c r="P23" t="n">
-        <v>416.7436576655219</v>
+        <v>416.6617780853886</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31331,28 +31455,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.086147090619975</v>
+        <v>-1.072851098670685</v>
       </c>
       <c r="J24" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K24" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4272396310304506</v>
+        <v>0.4208224352804976</v>
       </c>
       <c r="M24" t="n">
-        <v>8.528969857196484</v>
+        <v>8.570217501018401</v>
       </c>
       <c r="N24" t="n">
-        <v>109.3843045211379</v>
+        <v>110.1679139281434</v>
       </c>
       <c r="O24" t="n">
-        <v>10.4586951634101</v>
+        <v>10.49609041158389</v>
       </c>
       <c r="P24" t="n">
-        <v>418.3159821190719</v>
+        <v>418.1960502539732</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31409,28 +31533,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.314694039323607</v>
+        <v>-1.299688578943501</v>
       </c>
       <c r="J25" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K25" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5281594081545717</v>
+        <v>0.5211634025344685</v>
       </c>
       <c r="M25" t="n">
-        <v>8.282523441418155</v>
+        <v>8.343743733017661</v>
       </c>
       <c r="N25" t="n">
-        <v>106.7962398314574</v>
+        <v>107.9332888362706</v>
       </c>
       <c r="O25" t="n">
-        <v>10.33422661990037</v>
+        <v>10.38909470725292</v>
       </c>
       <c r="P25" t="n">
-        <v>416.0645079180735</v>
+        <v>415.9291563883107</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31487,28 +31611,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.344617620084843</v>
+        <v>-1.330617339652015</v>
       </c>
       <c r="J26" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K26" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4912273925069882</v>
+        <v>0.4857671077466271</v>
       </c>
       <c r="M26" t="n">
-        <v>9.257158279895917</v>
+        <v>9.307604366199547</v>
       </c>
       <c r="N26" t="n">
-        <v>129.5134984305553</v>
+        <v>130.3471335487871</v>
       </c>
       <c r="O26" t="n">
-        <v>11.38039974827578</v>
+        <v>11.41696691546345</v>
       </c>
       <c r="P26" t="n">
-        <v>406.6035453314358</v>
+        <v>406.4772606773373</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31565,28 +31689,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.04064439170978</v>
+        <v>-1.029974829177962</v>
       </c>
       <c r="J27" t="n">
+        <v>234</v>
+      </c>
+      <c r="K27" t="n">
         <v>233</v>
       </c>
-      <c r="K27" t="n">
-        <v>232</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.399677719029496</v>
+        <v>0.3953597055474031</v>
       </c>
       <c r="M27" t="n">
-        <v>8.512644044828772</v>
+        <v>8.541940998835262</v>
       </c>
       <c r="N27" t="n">
-        <v>112.8304992999164</v>
+        <v>113.155702307905</v>
       </c>
       <c r="O27" t="n">
-        <v>10.6221701784483</v>
+        <v>10.6374669121885</v>
       </c>
       <c r="P27" t="n">
-        <v>392.8776007403844</v>
+        <v>392.7814095765779</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31643,28 +31767,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9576652536061482</v>
+        <v>-0.9456635300307651</v>
       </c>
       <c r="J28" t="n">
+        <v>234</v>
+      </c>
+      <c r="K28" t="n">
         <v>233</v>
       </c>
-      <c r="K28" t="n">
-        <v>232</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.3755115852718339</v>
+        <v>0.3696354979818572</v>
       </c>
       <c r="M28" t="n">
-        <v>8.193777203473912</v>
+        <v>8.231244316644203</v>
       </c>
       <c r="N28" t="n">
-        <v>105.797595153322</v>
+        <v>106.3677316583415</v>
       </c>
       <c r="O28" t="n">
-        <v>10.28579579582066</v>
+        <v>10.31347330720071</v>
       </c>
       <c r="P28" t="n">
-        <v>385.8307825399264</v>
+        <v>385.7225813128415</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31721,28 +31845,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9135371025782348</v>
+        <v>-0.9003938866107916</v>
       </c>
       <c r="J29" t="n">
+        <v>234</v>
+      </c>
+      <c r="K29" t="n">
         <v>233</v>
       </c>
-      <c r="K29" t="n">
-        <v>232</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.3236611464988343</v>
+        <v>0.3172658951200452</v>
       </c>
       <c r="M29" t="n">
-        <v>8.433153883783818</v>
+        <v>8.471699774696013</v>
       </c>
       <c r="N29" t="n">
-        <v>120.9688186577014</v>
+        <v>121.6779330293188</v>
       </c>
       <c r="O29" t="n">
-        <v>10.99858257493671</v>
+        <v>11.0307720957927</v>
       </c>
       <c r="P29" t="n">
-        <v>378.7312515413129</v>
+        <v>378.6127592192238</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31799,28 +31923,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7696450918066149</v>
+        <v>-0.7573008832918311</v>
       </c>
       <c r="J30" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K30" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2536416264275722</v>
+        <v>0.247724500614092</v>
       </c>
       <c r="M30" t="n">
-        <v>8.320438812900322</v>
+        <v>8.35104638455906</v>
       </c>
       <c r="N30" t="n">
-        <v>120.5547101162388</v>
+        <v>121.1178806966276</v>
       </c>
       <c r="O30" t="n">
-        <v>10.97974089476791</v>
+        <v>11.00535690909784</v>
       </c>
       <c r="P30" t="n">
-        <v>373.3355917602024</v>
+        <v>373.2242451261195</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31877,28 +32001,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7822103293295207</v>
+        <v>-0.7688417273897193</v>
       </c>
       <c r="J31" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K31" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2778134379446476</v>
+        <v>0.2705982529664477</v>
       </c>
       <c r="M31" t="n">
-        <v>8.262317624348388</v>
+        <v>8.31033186589117</v>
       </c>
       <c r="N31" t="n">
-        <v>110.3739555741692</v>
+        <v>111.1717784153499</v>
       </c>
       <c r="O31" t="n">
-        <v>10.50590098821463</v>
+        <v>10.54380284410468</v>
       </c>
       <c r="P31" t="n">
-        <v>374.7446607338015</v>
+        <v>374.6238966051599</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31955,28 +32079,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6405966183803055</v>
+        <v>-0.6293518034225483</v>
       </c>
       <c r="J32" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K32" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2976446712966286</v>
+        <v>0.289536455142025</v>
       </c>
       <c r="M32" t="n">
-        <v>6.398381744732168</v>
+        <v>6.435889148853179</v>
       </c>
       <c r="N32" t="n">
-        <v>67.35758819804505</v>
+        <v>67.97092760950798</v>
       </c>
       <c r="O32" t="n">
-        <v>8.207166880114297</v>
+        <v>8.244448290183399</v>
       </c>
       <c r="P32" t="n">
-        <v>351.488340448998</v>
+        <v>351.3867574062273</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -32033,28 +32157,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4622286998644791</v>
+        <v>-0.4536179984775045</v>
       </c>
       <c r="J33" t="n">
+        <v>234</v>
+      </c>
+      <c r="K33" t="n">
         <v>233</v>
       </c>
-      <c r="K33" t="n">
-        <v>232</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.1714962746419233</v>
+        <v>0.1665503045631962</v>
       </c>
       <c r="M33" t="n">
-        <v>6.539347616523314</v>
+        <v>6.565392814562858</v>
       </c>
       <c r="N33" t="n">
-        <v>71.55998449456744</v>
+        <v>71.77980125223174</v>
       </c>
       <c r="O33" t="n">
-        <v>8.459313476551596</v>
+        <v>8.472296102723968</v>
       </c>
       <c r="P33" t="n">
-        <v>336.6299711560289</v>
+        <v>336.5522990370392</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -32111,28 +32235,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5099593079067931</v>
+        <v>-0.5011078267398806</v>
       </c>
       <c r="J34" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K34" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1121285316933427</v>
+        <v>0.1092564356882318</v>
       </c>
       <c r="M34" t="n">
-        <v>9.138906455313714</v>
+        <v>9.159830360763515</v>
       </c>
       <c r="N34" t="n">
-        <v>143.3716951663004</v>
+        <v>143.3132873164078</v>
       </c>
       <c r="O34" t="n">
-        <v>11.97379201282118</v>
+        <v>11.97135277720976</v>
       </c>
       <c r="P34" t="n">
-        <v>330.4735267907109</v>
+        <v>330.3938657956828</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -32189,28 +32313,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.08755636709239126</v>
+        <v>-0.08796399184104779</v>
       </c>
       <c r="J35" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K35" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002079674728723946</v>
+        <v>0.002119525497389141</v>
       </c>
       <c r="M35" t="n">
-        <v>12.93045957444393</v>
+        <v>12.87711108274844</v>
       </c>
       <c r="N35" t="n">
-        <v>256.9147841106076</v>
+        <v>255.803791486488</v>
       </c>
       <c r="O35" t="n">
-        <v>16.02856151095935</v>
+        <v>15.99386730864327</v>
       </c>
       <c r="P35" t="n">
-        <v>305.3093926272084</v>
+        <v>305.3130584646806</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -32248,7 +32372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ234"/>
+  <dimension ref="A1:AJ235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74655,6 +74779,188 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-34.50670656154249,172.70223495355268</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>-34.505913147850194,172.70238859248747</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-34.505196898987926,172.70216118943074</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-34.50449444495681,172.70186564301596</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-34.50379817471589,172.70153518880193</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-34.50312181564785,172.7011756165965</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-34.50248485285923,172.7007264399642</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-34.501872411413096,172.7002211998467</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-34.50129925441888,172.69964972730358</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-34.50071931714505,172.69908967753605</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-34.50012072917493,172.69856106156783</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>-34.499549081758445,172.69798702225194</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>-34.498991296030404,172.69738960768342</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>-34.498409187120416,172.6968331895778</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>-34.49782238615219,172.69629188673338</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>-34.49722225427756,172.69577598045942</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>-34.496613628722535,172.695264206207</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>-34.49602776076531,172.69471470203007</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>-34.495457957316404,172.69414096982172</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>-34.49490974340884,172.69353467888965</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>-34.494371560859186,172.69291325655252</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>-34.49384481900107,172.69227457771663</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>-34.49333097303125,172.6916653056381</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>-34.49280445034672,172.69108598519398</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>-34.492238116697614,172.69050283893446</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>-34.49168032432326,172.6899025699877</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>-34.491167778604996,172.6892534500838</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>-34.49064615345674,172.68861412927768</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>-34.490137319464615,172.68796130288524</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>-34.489675084010706,172.68727602841727</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>-34.48921536235052,172.68654591386004</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>-34.48882338241848,172.6857699511022</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>-34.488483942344665,172.6849678805951</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>-34.48798954959101,172.68424281094258</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
